--- a/ig/test-tabs-svs/ValueSet-jdv-j240-activite-sanitaire-diverse-regulee-finess.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j240-activite-sanitaire-diverse-regulee-finess.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2265" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="818">
   <si>
     <t>Property</t>
   </si>
@@ -128,7 +128,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee|20260601120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r347-activite-sanitaire-diverse-regulee|20260629120000</t>
   </si>
   <si>
     <t>version</t>
@@ -167,12 +167,24 @@
     <t>Accueil et Traitement des Urgences Médico-Chirurgicales</t>
   </si>
   <si>
+    <t>861</t>
+  </si>
+  <si>
+    <t>Accueil familial thérapeutique</t>
+  </si>
+  <si>
     <t>226</t>
   </si>
   <si>
     <t>Accueil Orientation. des Malades.Tuberculo Pulmonaires</t>
   </si>
   <si>
+    <t>863</t>
+  </si>
+  <si>
+    <t>Accueil permanent</t>
+  </si>
+  <si>
     <t>741</t>
   </si>
   <si>
@@ -311,6 +323,12 @@
     <t>Anesthésiologie &amp; Salle Réveil</t>
   </si>
   <si>
+    <t>862</t>
+  </si>
+  <si>
+    <t>Appartement thérapeutique</t>
+  </si>
+  <si>
     <t>647</t>
   </si>
   <si>
@@ -473,6 +491,12 @@
     <t>Centre AntiPoison</t>
   </si>
   <si>
+    <t>877</t>
+  </si>
+  <si>
+    <t>Centre d'accueil et de crise</t>
+  </si>
+  <si>
     <t>237</t>
   </si>
   <si>
@@ -497,12 +521,42 @@
     <t>Centre d'accueil thérapeutique à temps partiel infanto-juv</t>
   </si>
   <si>
+    <t>864</t>
+  </si>
+  <si>
+    <t>Centre d'activités thérapeutiques et de temps de groupe</t>
+  </si>
+  <si>
     <t>759</t>
   </si>
   <si>
     <t>Centre d'Hémobiologie</t>
   </si>
   <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>Centre de consultations</t>
+  </si>
+  <si>
+    <t>865</t>
+  </si>
+  <si>
+    <t>Centre de crise</t>
+  </si>
+  <si>
+    <t>866</t>
+  </si>
+  <si>
+    <t>Centre de soins post-aigus</t>
+  </si>
+  <si>
+    <t>867</t>
+  </si>
+  <si>
+    <t>Centre médico-psychologique</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
@@ -1307,6 +1361,18 @@
     <t>Hépato-Gastro-Entérologie</t>
   </si>
   <si>
+    <t>868</t>
+  </si>
+  <si>
+    <t>Hôpital de jour</t>
+  </si>
+  <si>
+    <t>874</t>
+  </si>
+  <si>
+    <t>Hôpital de nuit</t>
+  </si>
+  <si>
     <t>753</t>
   </si>
   <si>
@@ -2123,6 +2189,12 @@
     <t>service accueil et traitement urgences</t>
   </si>
   <si>
+    <t>869</t>
+  </si>
+  <si>
+    <t>Service médico-psychologique régional</t>
+  </si>
+  <si>
     <t>195</t>
   </si>
   <si>
@@ -2153,6 +2225,12 @@
     <t>soins intensifs de néonatologie</t>
   </si>
   <si>
+    <t>870</t>
+  </si>
+  <si>
+    <t>Soins à domicile</t>
+  </si>
+  <si>
     <t>143</t>
   </si>
   <si>
@@ -2301,6 +2379,30 @@
   </si>
   <si>
     <t>unité de proximité accueil traitement orientation urgences</t>
+  </si>
+  <si>
+    <t>876</t>
+  </si>
+  <si>
+    <t>Unité d’hospitalisation complète</t>
+  </si>
+  <si>
+    <t>871</t>
+  </si>
+  <si>
+    <t>Unité hospitalière spécialement aménagée</t>
+  </si>
+  <si>
+    <t>872</t>
+  </si>
+  <si>
+    <t>Unité pour malades difficiles</t>
+  </si>
+  <si>
+    <t>873</t>
+  </si>
+  <si>
+    <t>Unité sanitaire en milieu pénitentiaire</t>
   </si>
   <si>
     <t>307</t>
@@ -2716,7 +2818,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G370"/>
+  <dimension ref="A1:G387"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2802,7 +2904,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -2844,7 +2946,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -2886,7 +2988,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -2949,7 +3051,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -2970,7 +3072,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -3012,7 +3114,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -3138,7 +3240,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -3201,7 +3303,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -3222,7 +3324,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
@@ -3264,7 +3366,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -3348,7 +3450,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
@@ -3411,7 +3513,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -3432,7 +3534,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -3768,7 +3870,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51">
@@ -3831,7 +3933,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -3873,7 +3975,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56">
@@ -3894,7 +3996,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57">
@@ -3915,7 +4017,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58">
@@ -3978,7 +4080,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
@@ -3999,7 +4101,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62">
@@ -4041,7 +4143,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -4083,7 +4185,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66">
@@ -4104,7 +4206,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
@@ -4125,7 +4227,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
@@ -4146,7 +4248,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
@@ -4398,7 +4500,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81">
@@ -4419,7 +4521,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82">
@@ -4440,7 +4542,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">
@@ -4461,7 +4563,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84">
@@ -4524,7 +4626,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
@@ -4545,7 +4647,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
@@ -4566,7 +4668,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89">
@@ -4587,7 +4689,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90">
@@ -4608,7 +4710,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91">
@@ -4629,7 +4731,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -4650,7 +4752,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -4713,7 +4815,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -4734,7 +4836,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -4755,7 +4857,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
@@ -5343,7 +5445,7 @@
         <v>15</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126">
@@ -5532,7 +5634,7 @@
         <v>15</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135">
@@ -5784,7 +5886,7 @@
         <v>15</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147">
@@ -5805,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="148">
@@ -5973,7 +6075,7 @@
         <v>15</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="156">
@@ -5994,7 +6096,7 @@
         <v>15</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157">
@@ -6393,7 +6495,7 @@
         <v>15</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="176">
@@ -6414,7 +6516,7 @@
         <v>15</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="177">
@@ -6582,7 +6684,7 @@
         <v>15</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185">
@@ -6792,7 +6894,7 @@
         <v>15</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="195">
@@ -6897,7 +6999,7 @@
         <v>15</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="200">
@@ -6939,7 +7041,7 @@
         <v>15</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="202">
@@ -6981,7 +7083,7 @@
         <v>15</v>
       </c>
       <c r="G203" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="204">
@@ -7002,7 +7104,7 @@
         <v>15</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="205">
@@ -7128,7 +7230,7 @@
         <v>15</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="211">
@@ -7170,7 +7272,7 @@
         <v>15</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="213">
@@ -7212,7 +7314,7 @@
         <v>15</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="215">
@@ -7443,7 +7545,7 @@
         <v>15</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="226">
@@ -7632,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="235">
@@ -7653,7 +7755,7 @@
         <v>15</v>
       </c>
       <c r="G235" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="236">
@@ -7674,7 +7776,7 @@
         <v>15</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="237">
@@ -7695,7 +7797,7 @@
         <v>15</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="238">
@@ -7863,7 +7965,7 @@
         <v>15</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246">
@@ -7884,7 +7986,7 @@
         <v>15</v>
       </c>
       <c r="G246" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247">
@@ -7905,7 +8007,7 @@
         <v>15</v>
       </c>
       <c r="G247" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="248">
@@ -7926,7 +8028,7 @@
         <v>15</v>
       </c>
       <c r="G248" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="249">
@@ -8199,7 +8301,7 @@
         <v>15</v>
       </c>
       <c r="G261" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="262">
@@ -8304,7 +8406,7 @@
         <v>15</v>
       </c>
       <c r="G266" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="267">
@@ -8325,7 +8427,7 @@
         <v>15</v>
       </c>
       <c r="G267" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="268">
@@ -8451,7 +8553,7 @@
         <v>15</v>
       </c>
       <c r="G273" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="274">
@@ -8535,7 +8637,7 @@
         <v>15</v>
       </c>
       <c r="G277" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="278">
@@ -8556,7 +8658,7 @@
         <v>15</v>
       </c>
       <c r="G278" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="279">
@@ -8682,7 +8784,7 @@
         <v>15</v>
       </c>
       <c r="G284" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="285">
@@ -9879,7 +9981,7 @@
         <v>15</v>
       </c>
       <c r="G341" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="342">
@@ -10005,7 +10107,7 @@
         <v>15</v>
       </c>
       <c r="G347" t="s" s="2">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="348">
@@ -10236,7 +10338,7 @@
         <v>15</v>
       </c>
       <c r="G358" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="359">
@@ -10383,7 +10485,7 @@
         <v>15</v>
       </c>
       <c r="G365" t="s" s="2">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="366">
@@ -10488,6 +10590,363 @@
         <v>15</v>
       </c>
       <c r="G370" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B371" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C371" s="2"/>
+      <c r="D371" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="E371" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="F371" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G371" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B372" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C372" s="2"/>
+      <c r="D372" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="E372" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="F372" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G372" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B373" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C373" s="2"/>
+      <c r="D373" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="E373" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="F373" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G373" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B374" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C374" s="2"/>
+      <c r="D374" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="E374" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="F374" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G374" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B375" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C375" s="2"/>
+      <c r="D375" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="E375" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="F375" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G375" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B376" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C376" s="2"/>
+      <c r="D376" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="E376" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="F376" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G376" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B377" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C377" s="2"/>
+      <c r="D377" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="E377" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="F377" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G377" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B378" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C378" s="2"/>
+      <c r="D378" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="E378" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="F378" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G378" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B379" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C379" s="2"/>
+      <c r="D379" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="E379" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="F379" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G379" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B380" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C380" s="2"/>
+      <c r="D380" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="E380" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="F380" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G380" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B381" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C381" s="2"/>
+      <c r="D381" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="E381" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="F381" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G381" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B382" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C382" s="2"/>
+      <c r="D382" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="E382" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="F382" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G382" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B383" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C383" s="2"/>
+      <c r="D383" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="E383" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="F383" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G383" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B384" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C384" s="2"/>
+      <c r="D384" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="E384" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="F384" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G384" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B385" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C385" s="2"/>
+      <c r="D385" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="E385" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="F385" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G385" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B386" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C386" s="2"/>
+      <c r="D386" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="E386" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="F386" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G386" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B387" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C387" s="2"/>
+      <c r="D387" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="E387" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="F387" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G387" t="s" s="2">
         <v>32</v>
       </c>
     </row>
